--- a/EXCEL/SILENT_Object_Datatable.xlsx
+++ b/EXCEL/SILENT_Object_Datatable.xlsx
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ANCHOR ID (카드 프리팹 앵커 2199)</t>
+          <t>ANCHOR ID (카드 프리팹 앵커 2237)</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>한 행 = 카드 한 장. 카드 50장은 앵커 2199(R01_FloorCard_Anchor)에 스폰되는 프리팹 하나 안에 들어 있어서 모든 행의 AnchorRef가 2199이고, CardNo 1~50이 프리팹 안 카드 순서(자식 오브젝트 이름 끝 번호, 예: Card_01)다. 정답 카드 4장(IsAnswer = Y)만 위가 글자, 아래가 1~9. 오답 카드 위에는 정답 글자 A · K · R · W를 쓰지 않는다. 기호는 Symbol 단어로 쓴다.</t>
+          <t>한 행 = 카드 한 장. 카드 50장은 앵커 2237(R01A_CardsPoint)에 스폰되는 프리팹 하나 안에 들어 있어서 모든 행의 AnchorRef가 2237이고, CardNo 1~50이 프리팹 안 카드 순서(자식 오브젝트 이름 끝 번호, 예: Card_01)다. 정답 카드 4장(IsAnswer = Y)만 위가 글자, 아래가 1~9. 오답 카드 위에는 정답 글자 A · K · R · W를 쓰지 않는다. 기호는 Symbol 단어로 쓴다.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT 2199의 자식. 카드 프리팹이 스폰될 때 ScreenText가 CardNo 순서대로 TopMark · BottomMark를 그린다. 서버 판정은 이 시트를 읽지 않는다(PUZZLE_SLOT).</t>
+          <t>ANCHOR_NONINTERACT 2237의 자식. 카드 프리팹이 스폰될 때 ScreenText가 CardNo 순서대로 TopMark · BottomMark를 그린다. 서버 판정은 이 시트를 읽지 않는다(PUZZLE_SLOT).</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>1</v>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>3</v>
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>4</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>5</v>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>6</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>7</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>8</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>9</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>10</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>11</v>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>12</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>13</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>14</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>16</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>17</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>18</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>19</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>20</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>21</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>22</v>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>23</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>24</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>25</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>26</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>27</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>28</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>29</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>30</v>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>31</v>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>32</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>33</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>34</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>35</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>36</v>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>37</v>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>38</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>39</v>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>40</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>41</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>42</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>43</v>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>44</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>45</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>46</v>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>47</v>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D54" s="8" t="n">
         <v>48</v>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>49</v>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>2199</v>
+        <v>2249</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>50</v>

--- a/EXCEL/SILENT_Object_Datatable.xlsx
+++ b/EXCEL/SILENT_Object_Datatable.xlsx
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" style="10" min="1" max="1"/>
@@ -982,31 +982,6 @@
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>IsAnswer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2049</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 종이</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>C BlackDiamond A = 64</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>A + B = 14</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" style="10" min="1" max="1"/>
@@ -1131,342 +1106,6 @@
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>IsAnswer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2056</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2057</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>2058</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>2059</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>2060</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>2061</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>2062</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>2063</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>2064</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>2065</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>2066</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>2067</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>B 6번 방 켜진 TV</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" style="10" min="1" max="1"/>
@@ -5090,681 +4729,6 @@
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>IsAnswer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2125</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 01</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2126</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>2127</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 03</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>2128</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 04</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>2129</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 05</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>2130</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 06</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>2131</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 07</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>2132</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 08</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>2133</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 09</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>2134</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 10</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>2135</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 11</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>2136</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 12</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>2137</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 13</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>2138</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 14</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>2139</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 15</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>2140</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 16</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>2141</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 17</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>2142</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 18</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>2143</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 19</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>2144</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 20</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>2145</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 21</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>2146</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 22</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>2147</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 23</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>2148</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 24</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>2149</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 25</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Teal</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>2150</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 26</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Teal</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
-        <v>2152</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>B 2번 방 액자 28</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
@@ -5791,7 +4755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" style="10" min="1" max="1"/>
@@ -5884,236 +4848,6 @@
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>IsAnswer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2183</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 01</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2184</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>2185</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 03</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>2186</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 04</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>2187</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 05</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>2188</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 06</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>2189</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 07</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>2190</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 08</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>2191</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 09</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>2192</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>A 3번 방 단서 화살표 10</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
     </row>
@@ -6140,7 +4874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" style="10" min="1" max="1"/>
@@ -6240,266 +4974,6 @@
         <is>
           <t>Port</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2153</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 01 (정답)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2154</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 02 (정답)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>2155</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 03 (정답)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>2156</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 04 (정답)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>2157</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 05 (정답)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>SkyBlue</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>2158</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 06 (가짜)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>2159</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 07 (가짜)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>2160</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 08 (가짜)</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>2161</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 09 (가짜)</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>2162</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>B 4번 방 전선 10 (가짜)</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6525,7 +4999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" style="10" min="1" max="1"/>
@@ -6631,706 +5105,6 @@
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Expression</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2163</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 01 (진짜 정의)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>BlackDiamond</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = a^2 - b^2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2164</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>WhiteDiamond</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = a^2 + b^2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>2165</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 03</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>BlackSpade</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = 2a + b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>2166</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 04</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>WhiteSpade</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = a * b - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>2167</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 05</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>(a + b)^2 = a^2 + 2ab + b^2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>2168</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 06</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Linear</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2x + 3 = 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>2169</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 07</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Linear</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>y = 3x - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>2170</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 08</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>BlackHeart</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Linear</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = (a - b) / 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>2171</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 09</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Quadratic</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>x^2 - 5x + 6 = 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>2172</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 10</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>WhiteHeart</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Quadratic</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = a^2 - 2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>2173</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 11</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Quadratic</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>x = (-b + sqrt(b^2 - 4ac)) / 2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>2174</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 12</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Cubic</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>x^3 - 1 = (x - 1)(x^2 + x + 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>2175</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 13</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>WhiteSpade</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Cubic</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = a^3 - b^3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>2176</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 14</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>a^2 + b^2 = c^2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>2177</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 15</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>sin^2 x + cos^2 x = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>2178</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 16</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>log2 8 = 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>2179</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 17</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Discrete</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>nCr = n! / (r! (n - r)!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>2180</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 18</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Discrete</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>n(P(S)) = 2^n</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>2181</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 19</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>BlackHeart</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Discrete</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = a mod b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>2182</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>A 5번 방 공식판 20</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>WhiteHeart</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>a [S] b = (a + b)^2</t>
         </is>
       </c>
     </row>
